--- a/config/rules/CRS610_MI.xlsx
+++ b/config/rules/CRS610_MI.xlsx
@@ -514,12 +514,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AACB</t>
+          <t>ACRF</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bank account number - bank giro</t>
+          <t>User-defined accounting control object</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -549,19 +549,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>8.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ACGR</t>
+          <t>CUST</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Object access group</t>
+          <t>Statistics customer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -598,12 +598,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACHK</t>
+          <t>RAN1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Assortment check</t>
+          <t>Fixed due date</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -645,12 +645,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ACLB</t>
+          <t>RAN2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -670,29 +670,34 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Clearing number</t>
+          <t>Fixed due date</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ACRF</t>
+          <t>RAN3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,29 +717,34 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>User-defined accounting control object</t>
+          <t>Fixed due date</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AGAC</t>
+          <t>RAN4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -754,29 +764,34 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Bank account number - postal giro</t>
+          <t>Fixed due date</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AGBG</t>
+          <t>SPLE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -796,34 +811,29 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Bank giro number</t>
+          <t>SPLC Code</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>10.0</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AGBP</t>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -843,7 +853,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Payer - bank giro</t>
+          <t>City</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -853,24 +863,29 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>20.0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AGCA</t>
+          <t>ADID</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>OKADID</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -880,44 +895,44 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKADID</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Cancellation</t>
+          <t>Address number</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AGCH</t>
+          <t>ALCU</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>OKALCU</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -927,44 +942,44 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKALCU</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Agreement check - order header</t>
+          <t>Search key</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AGCP</t>
+          <t>BLAC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>CONST</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -974,39 +989,49 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Constant: 0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Clearing number</t>
+          <t>Advice code</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AGCT</t>
+          <t>BLCD</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>OKBLCD</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1016,12 +1041,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKBLCD</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Agreement check - order lines</t>
+          <t>Customer stop</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1043,17 +1068,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AGPG</t>
+          <t>BLPR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>CONST</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1063,12 +1093,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Constant: 1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Postal giro number</t>
+          <t>Payment reminder code</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1078,7 +1108,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1090,17 +1120,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AGPN</t>
+          <t>CCUS</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>OKCCUS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1110,12 +1145,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKCCUS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Personal ID</t>
+          <t>Company group customer number</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1125,24 +1160,29 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AGPY</t>
+          <t>CDRC</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>OKCDRC</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1152,12 +1192,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKCDRC</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Payer - postal giro</t>
+          <t>Credit department reference</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1167,24 +1207,29 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AGTD</t>
+          <t>CFC6</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>OCUSMA/ OKCFC6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1194,44 +1239,44 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OCUSMA/ OKCFC6</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Transmission date</t>
+          <t>User-defined field 6 - customer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AGTN</t>
+          <t>CLCD</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>CONST</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1241,12 +1286,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Constant: 1</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Transmission number</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1256,7 +1301,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1268,17 +1313,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ALWT</t>
+          <t>CRL2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>OKCRL2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1288,12 +1338,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKCRL2</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Alias category</t>
+          <t>Credit limit 2</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1303,29 +1353,34 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>2.0</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ATPR</t>
+          <t>CRL3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>OKCRL3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1335,39 +1390,49 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKCRL3</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Attribute pricing rule</t>
+          <t>Credit limit 3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BCKO</t>
+          <t>CRLM</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>OKCRLM</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1377,12 +1442,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKCRLM</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Backorder</t>
+          <t>Credit limit 1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1392,29 +1457,34 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BOP1</t>
+          <t>CRTP</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>CONST</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>01</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1424,39 +1494,49 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Constant: 01</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Automatic Closing</t>
+          <t>Exchange rate type</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BUSE</t>
+          <t>CSCD</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>OKCSCD</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1466,44 +1546,44 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKCSCD</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bonus and/or commission active</t>
+          <t>County</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>40.0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CFC0</t>
+          <t>CUA1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>OKCUA1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1513,12 +1593,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKCUA1</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>User-defined field 10 - customer</t>
+          <t>Address line 1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1528,24 +1608,29 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>36.0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CFC1</t>
+          <t>CUA2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>OKCUA2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1555,12 +1640,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKCUA2</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>User-defined field 1 - customer</t>
+          <t>Address line 2</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1570,24 +1655,29 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>36.0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CFC2</t>
+          <t>CUA3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>OKCUA3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1597,44 +1687,44 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKCUA3</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>User-defined field 2 - customer</t>
+          <t>Address line 3</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>2.0</t>
+          <t>36.0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CFC3</t>
+          <t>CUA4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>OKCUA4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1644,12 +1734,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKCUA4</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>User-defined field 3 - customer</t>
+          <t>Address line 4</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1659,24 +1749,34 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>36.0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CFC4</t>
+          <t>CUCD</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>OKCUCD</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>MAP</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>CRS055-Currency-CUCD.xlsx</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1686,12 +1786,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Lookup Table: CRS055-Currency-CUCD.xlsx</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>User-defined field 4 - customer</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1701,24 +1801,29 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CFC5</t>
+          <t>CUNM</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>OKCUNM</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1728,12 +1833,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKCUNM</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>User-defined field 5 - customer</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1743,24 +1848,29 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>36.0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CFC7</t>
+          <t>CUNO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>OKCUNO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1770,44 +1880,44 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKCUNO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>User-defined field 7 - customer</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CFC8</t>
+          <t>CUTP</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>CONST</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0 - Normal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1817,39 +1927,49 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Constant: 0 - Normal</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>User-defined field 8 - customer</t>
+          <t>Customer type</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CFC9</t>
+          <t>DESV</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>CONST</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>GB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1859,12 +1979,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Constant: GB</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>User-defined field 9 - customer</t>
+          <t>Alternate lang for option description</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1874,24 +1994,29 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CHSY</t>
+          <t>DOGR</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>OKDOGR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1901,12 +2026,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKDOGR</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Line charge model</t>
+          <t>Customer document group</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1916,24 +2041,29 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CUCL</t>
+          <t>DTFM</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>CONST</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>YMD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1943,12 +2073,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Constant: YMD</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Customer group</t>
+          <t>Date format</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1965,17 +2095,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CUST</t>
+          <t>DUCD</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>OKDUCD</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1985,39 +2120,49 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKDUCD</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Statistics customer</t>
+          <t>Due date base</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CUSU</t>
+          <t>ECAR</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>OKECAR</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2027,12 +2172,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKECAR</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Our supplier number at customer</t>
+          <t>State</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2042,24 +2187,29 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DIGC</t>
+          <t>EDES</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>OKEDES</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2069,12 +2219,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKEDES</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Discount group - customer</t>
+          <t>Place</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2084,24 +2234,30 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DISY</t>
+          <t>EDIT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>CONST</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>/
+ria to update the template /</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2111,12 +2267,13 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Constant: /
+ria to update the template /</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Discount model</t>
+          <t>Date editing</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2126,24 +2283,29 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DTE1</t>
+          <t>FACI</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>OKFACI</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2153,44 +2315,44 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKFACI</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Change date - credit limit 1</t>
+          <t>Facility</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DTE2</t>
+          <t>FRE1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>OKFRE1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2200,44 +2362,44 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKFRE1</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Change date - credit limit 2</t>
+          <t>Statistics identity 1 customer</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DTE3</t>
+          <t>GEOC</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>OKGEOC</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2247,12 +2409,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKGEOC</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Change date - credit limit 3</t>
+          <t>Geographical code</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2262,7 +2424,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2274,17 +2436,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EALO</t>
+          <t>GRPY</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>CONST</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2294,12 +2461,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Constant: 0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>EAN location code</t>
+          <t>Group invoice</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2309,7 +2476,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2321,17 +2488,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EXCD</t>
+          <t>HAFE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>OKHAFE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2341,39 +2513,34 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKHAFE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Service charge</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2.0</t>
+          <t>Harbor Airport</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FRE2</t>
+          <t>LHCD</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>OKLHCD</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2383,12 +2550,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKLHCD</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Statistics identity 2 customer</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2398,24 +2565,29 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ININ</t>
+          <t>MODL</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>OCUSMA SPREADSHEET</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2425,44 +2597,44 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OCUSMA SPREADSHEET</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Invoicing Interval</t>
+          <t>Delivery method</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>3.0</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IVGP</t>
+          <t>ODUD</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>OKODUD</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2472,39 +2644,49 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKODUD</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Invoicing group</t>
+          <t>Credit limit 4</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>3.0</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LSID</t>
+          <t>OPAY</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>CONST</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2514,12 +2696,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Constant: 0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>AP Payout</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2529,24 +2711,34 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MCOS</t>
+          <t>ORTP</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>OKORTP</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2556,44 +2748,44 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKORTP</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>CO number mandatory</t>
+          <t>Customer order type</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OREF</t>
+          <t>PHN2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>OKPHN2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2603,12 +2795,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKPHN2</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Our reference</t>
+          <t>Telephone number 2</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2618,24 +2810,29 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>16.0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PADL</t>
+          <t>PHNO</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>OKPHNO</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2645,44 +2842,44 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKPHNO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Partial delivery</t>
+          <t>Telephone number 1</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PLTB</t>
+          <t>PONO</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>OKPONO</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2692,12 +2889,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKPONO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Price list table</t>
+          <t>Postal code</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2714,17 +2911,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>POPN</t>
+          <t>PYCD</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>OKPYCD</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>MAP</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>CRS076-AR Payment Method (for customers)-PYCD.xlsx</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2734,12 +2941,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Lookup Table: CRS076-AR Payment Method (for customers)-PYCD.xlsx</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Alias number</t>
+          <t>Payment method - accounts receivable</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2749,24 +2956,29 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PRDL</t>
+          <t>PYNO</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>OKPYNO</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2776,44 +2988,44 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKPYNO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Print delivery information</t>
+          <t>Payer</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PRIO</t>
+          <t>RESP</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>OKRESP</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2823,44 +3035,44 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKRESP</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Responsible</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PRVG</t>
+          <t>RMCT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>CONST</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Z01</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2870,12 +3082,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Constant: Z01</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Commission group</t>
+          <t>Payment reminder rule</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2885,24 +3097,29 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PYOP</t>
+          <t>SDST</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>OKSDST</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2912,44 +3129,44 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKSDST</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Search path - payer</t>
+          <t>District</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RAN1</t>
+          <t>SMCD</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>OKSMCD</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2959,44 +3176,44 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKSMCD</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fixed due date</t>
+          <t>Salesperson</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RAN2</t>
+          <t>STAT</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>OKSTAT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3006,44 +3223,44 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKSTAT</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Fixed due date</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>2.0</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RAN3</t>
+          <t>STMR</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>CONST</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3053,44 +3270,44 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Constant: 30</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Fixed due date</t>
+          <t>Statement rule</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RAN4</t>
+          <t>STMS</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>CONST</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3100,12 +3317,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Constant: 3</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Fixed due date</t>
+          <t>Statement code</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3115,7 +3332,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3127,17 +3344,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SPLE</t>
+          <t>TAXC</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>OKTAXC</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3147,12 +3369,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKTAXC</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SPLC Code</t>
+          <t>Tax code customer/address</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3162,24 +3384,29 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SPLM</t>
+          <t>TECD</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>OKTECD</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3189,12 +3416,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKTECD</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Supply model</t>
+          <t>Cash discount term</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3204,24 +3431,29 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TCEX</t>
+          <t>TECN</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>OKTECN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3231,44 +3463,44 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKTECN</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Included in business chain</t>
+          <t>Tax exemption contract number</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TEEC</t>
+          <t>TEDL</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>OKTEDL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3278,44 +3510,49 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKTEDL</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Tax exemption expiry date</t>
+          <t>Delivery terms</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TOWN</t>
+          <t>TEPA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>OKTEPA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>MAP</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>CRS125-Packaging Term-TEPA.xlsx</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3325,12 +3562,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Lookup Table: CRS125-Packaging Term-TEPA.xlsx</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Packaging terms</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3340,24 +3577,29 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ULZO</t>
+          <t>TEPY</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>OKTEPY</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3367,12 +3609,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKTEPY</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Unloading zone</t>
+          <t>Payment terms</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3382,24 +3624,29 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>USR1</t>
+          <t>TFNO</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>OKTFNO</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3409,12 +3656,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKTFNO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Credit limit 1 changed by</t>
+          <t>Facsimile transmission number</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3424,24 +3671,29 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>16.0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>USR2</t>
+          <t>TINC</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>CONST</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Pricelist does not always include tax, so this should always be 0,  unticked</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3451,39 +3703,49 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Constant: Pricelist does not always include tax, so this should always be 0,  unticked</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Credit limit 2 changed by</t>
+          <t>VAT included</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>USR3</t>
+          <t>TXAP</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>CONST</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3493,39 +3755,49 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Constant: 1</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Credit limit 3 changed by</t>
+          <t>Tax applicable</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VDLA</t>
+          <t>VRNO</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>OKVRNO</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3535,44 +3807,49 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Mapped from OKVRNO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Display valid delivery addresses</t>
+          <t>VAT registration number</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>YRE2</t>
+          <t>VTCD</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>OKVTCD</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>MAP</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>CRS030-VAT Code-VTCD.xlsx</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3582,39 +3859,44 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required! Logic: </t>
+          <t>Lookup Table: CRS030-VAT Code-VTCD.xlsx</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Your reference 2</t>
+          <t>VAT code</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ADBO</t>
+          <t>WHLO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>OKADBO</t>
+          <t>OKWHLO</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3629,44 +3911,39 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Mapped from OKADBO</t>
+          <t>Mapped from OKWHLO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Separate invoices</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ADCA</t>
+          <t>YREF</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>OKADCA</t>
+          <t>OCUSMA SHEET OKYREF - YOUR REFERENCE 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3681,12 +3958,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Mapped from OKADCA</t>
+          <t>Mapped from OCUSMA SHEET OKYREF - YOUR REFERENCE 1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Advice rule</t>
+          <t>Your reference 1</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3696,29 +3973,19 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>30.0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ADID</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>OKADID</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
+          <t>AACB</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3726,14 +3993,9 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Mapped from OKADID</t>
-        </is>
-      </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Address number</t>
+          <t>Bank account number - bank giro</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3743,29 +4005,24 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>12.0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ALCU</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>OKALCU</t>
+          <t>ACEI</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3775,44 +4032,44 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Mapped from OKALCU</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Search key</t>
+          <t>Advance invoicing of ECI</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BGRP</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>OKCFC8</t>
+          <t>ACGR</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3822,12 +4079,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Mapped from OKCFC8</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Bonus group</t>
+          <t>Object access group</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3837,29 +4094,24 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BLAC</t>
+          <t>ACHK</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CONST</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3869,12 +4121,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Constant: 0</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Advice code</t>
+          <t>Assortment check</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3896,22 +4148,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BLCD</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>OKBLCD</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
+          <t>ACLB</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3919,51 +4161,36 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Mapped from OKBLCD</t>
-        </is>
-      </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Customer stop</t>
+          <t>Clearing number</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BLII</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>OKBLII</t>
+          <t>ADBO</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3973,12 +4200,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Mapped from OKBLII</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Interest invoicing</t>
+          <t>Separate invoices</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4000,22 +4227,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BLPR</t>
+          <t>ADCA</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CONST</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4025,49 +4247,39 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Constant: 1</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Payment reminder code</t>
+          <t>Advice rule</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CCUS</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>OKCCUS</t>
+          <t>ADVI</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4077,12 +4289,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Mapped from OKCCUS</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Company group customer number</t>
+          <t>Ship-via address</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4092,29 +4304,19 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>6.0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CDRC</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>OKCDRC</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
+          <t>AGAC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4122,14 +4324,9 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Mapped from OKCDRC</t>
-        </is>
-      </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Credit department reference</t>
+          <t>Bank account number - postal giro</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4139,29 +4336,19 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>12.0</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CFC6</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>OCUSMA/ OKCFC6</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
+          <t>AGBG</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4169,46 +4356,36 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Mapped from OCUSMA/ OKCFC6</t>
-        </is>
-      </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>User-defined field 6 - customer</t>
+          <t>Bank giro number</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
           <t>10.0</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CLCD</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>CONST</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>AGBP</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4216,51 +4393,31 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Constant: 1</t>
-        </is>
-      </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Payer - bank giro</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>COR2</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>OKCOR2</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
+          <t>AGCA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4268,46 +4425,41 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Mapped from OKCOR2</t>
-        </is>
-      </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Organization number 2</t>
+          <t>Cancellation</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CORG</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>OKCORG</t>
+          <t>AGCH</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4317,44 +4469,39 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Mapped from OKCORG</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Organization number 1</t>
+          <t>Agreement check - order header</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CRL2</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>OKCRL2</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
+          <t>AGCP</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4362,51 +4509,36 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Mapped from OKCRL2</t>
-        </is>
-      </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Credit limit 2</t>
+          <t>Clearing number</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CRL3</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>OKCRL3</t>
+          <t>AGCT</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4416,12 +4548,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Mapped from OKCRL3</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Credit limit 3</t>
+          <t>Agreement check - order lines</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,34 +4563,24 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CRLM</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>OKCRLM</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
+          <t>AGPG</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4466,14 +4588,9 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Mapped from OKCRLM</t>
-        </is>
-      </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Credit limit 1</t>
+          <t>Postal giro number</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4483,34 +4600,24 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CRTP</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>CONST</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>01</t>
+          <t>AGPN</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4518,51 +4625,31 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Constant: 01</t>
-        </is>
-      </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Exchange rate type</t>
+          <t>Personal ID</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CSCD</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>OKCSCD</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
+          <t>AGPY</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4570,14 +4657,9 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Mapped from OKCSCD</t>
-        </is>
-      </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>County</t>
+          <t>Payer - postal giro</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4587,29 +4669,19 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>18.0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CUA1</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>OKCUA1</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
+          <t>AGTD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4617,46 +4689,36 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Mapped from OKCUA1</t>
-        </is>
-      </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Address line 1</t>
+          <t>Transmission date</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CUA2</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>OKCUA2</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
+          <t>AGTN</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4664,46 +4726,41 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Mapped from OKCUA2</t>
-        </is>
-      </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Address line 2</t>
+          <t>Transmission number</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CUA3</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>OKCUA3</t>
+          <t>AICD</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4713,44 +4770,44 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Mapped from OKCUA3</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Address line 3</t>
+          <t>Summary invoice</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CUA4</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>OKCUA4</t>
+          <t>ALWT</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4760,49 +4817,44 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Mapped from OKCUA4</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Address line 4</t>
+          <t>Alias category</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CUCD</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>OKCUCD</t>
+          <t>AOTP</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>MAP</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>CRS055-Currency-CUCD.xlsx</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4812,12 +4864,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lookup Table: CRS055-Currency-CUCD.xlsx</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Agreement order type</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4834,22 +4886,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CUIC</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>OKCUIC</t>
+          <t>ATPR</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4859,12 +4906,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Mapped from OKCUIC</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Customer number at the insurance company</t>
+          <t>Attribute pricing rule</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4874,29 +4921,24 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CUNM</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>OKCUNM</t>
+          <t>BCKO</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4906,44 +4948,44 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Mapped from OKCUNM</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Backorder</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CUNO</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>OKCUNO</t>
+          <t>BGRP</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4953,12 +4995,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Mapped from OKCUNO</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Bonus group</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4968,29 +5010,24 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CUTP</t>
+          <t>BLII</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>CONST</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>0 - Normal</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5000,12 +5037,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Constant: 0 - Normal</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Customer type</t>
+          <t>Interest invoicing</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5027,22 +5064,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DESV</t>
+          <t>BOP1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>CONST</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>GB</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5052,12 +5084,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Constant: GB</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Alternate lang for option description</t>
+          <t>Automatic Closing</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5067,29 +5099,24 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DOGR</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>OKDOGR</t>
+          <t>BPCD</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5099,44 +5126,44 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Mapped from OKDOGR</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Customer document group</t>
+          <t>Buying pattern type</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DTFM</t>
+          <t>BPEX</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>CONST</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>YMD</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5146,44 +5173,44 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Constant: YMD</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Date format</t>
+          <t>Buying pattern exception</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DTL2</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>OKDTL2</t>
+          <t>BUSE</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5193,12 +5220,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Mapped from OKDTL2</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Change date insurance limit</t>
+          <t>Bonus and/or commission active</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5208,7 +5235,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -5220,22 +5247,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DUCD</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>OKDUCD</t>
+          <t>CFC0</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5245,49 +5267,39 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Mapped from OKDUCD</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Due date base</t>
+          <t>User-defined field 10 - customer</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
           <t>1.0</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ECAR</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>OKECAR</t>
+          <t>CFC1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5297,12 +5309,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Mapped from OKECAR</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>User-defined field 1 - customer</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5312,29 +5324,24 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EDES</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>OKEDES</t>
+          <t>CFC2</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5344,45 +5351,44 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Mapped from OKEDES</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Place</t>
+          <t>User-defined field 2 - customer</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EDIT</t>
+          <t>CFC3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>CONST</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>/
-ria to update the template /</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5392,13 +5398,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Constant: /
-ria to update the template /</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Date editing</t>
+          <t>User-defined field 3 - customer</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5408,29 +5413,24 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>FACI</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>OKFACI</t>
+          <t>CFC4</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Mapped from OKFACI</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Facility</t>
+          <t>User-defined field 4 - customer</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5455,29 +5455,24 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>FRE1</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>OKFRE1</t>
+          <t>CFC5</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5487,12 +5482,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Mapped from OKFRE1</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Statistics identity 1 customer</t>
+          <t>User-defined field 5 - customer</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5502,29 +5497,24 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>GEOC</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>OKGEOC</t>
+          <t>CFC7</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5534,12 +5524,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Mapped from OKGEOC</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Geographical code</t>
+          <t>User-defined field 7 - customer</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5549,34 +5539,29 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GRPY</t>
+          <t>CFC8</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>CONST</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5586,49 +5571,39 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Constant: 0</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Group invoice</t>
+          <t>User-defined field 8 - customer</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HAFE</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>OKHAFE</t>
+          <t>CFC9</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5638,34 +5613,39 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Mapped from OKHAFE</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Harbor Airport</t>
+          <t>User-defined field 9 - customer</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>IICT</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>OKIICT</t>
+          <t>CHSY</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5675,12 +5655,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Mapped from OKIICT</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Interest rule</t>
+          <t>Line charge model</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5690,29 +5670,24 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>INCO</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>OKINCO</t>
+          <t>COR2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5722,12 +5697,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Mapped from OKINCO</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Insurance company</t>
+          <t>Organization number 2</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5737,29 +5712,24 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>11.0</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>INLI</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>OKINLI</t>
+          <t>CORG</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5769,49 +5739,39 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Mapped from OKINLI</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Insurance limit</t>
+          <t>Organization number 1</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>2.0</t>
+          <t>11.0</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>INRC</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>OKINRC</t>
+          <t>CUCL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5821,12 +5781,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Mapped from OKINRC</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Invoice recipient</t>
+          <t>Customer group</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5836,29 +5796,24 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>INSN</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>OKINSN</t>
+          <t>CUIC</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5868,12 +5823,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Mapped from OKINSN</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Insurance number</t>
+          <t>Customer number at the insurance company</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5883,29 +5838,24 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>INSS</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>OKINSS</t>
+          <t>CUSU</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5915,49 +5865,34 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Mapped from OKINSS</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Insurance status</t>
+          <t>Our supplier number at customer</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>LHCD</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>OKLHCD</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
+          <t>CUTM</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5965,46 +5900,26 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Mapped from OKLHCD</t>
-        </is>
-      </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>2.0</t>
+          <t>Copy</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>MODL</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>OCUSMA SPREADSHEET</t>
+          <t>DIGC</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6014,12 +5929,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Mapped from OCUSMA SPREADSHEET</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Delivery method</t>
+          <t>Discount group - customer</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6029,29 +5944,24 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NALI</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>OKNALI</t>
+          <t>DISY</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6061,49 +5971,39 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Mapped from OKNALI</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Unapproved limit</t>
+          <t>Discount model</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ODUD</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>OKODUD</t>
+          <t>DPOT</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6113,17 +6013,17 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Mapped from OKODUD</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Credit limit 4</t>
+          <t>Rental depot</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -6140,22 +6040,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ODUE</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>OKODUE</t>
+          <t>DTE1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6165,12 +6060,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Mapped from OKODUE</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Number of overdue days</t>
+          <t>Change date - credit limit 1</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6180,7 +6075,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -6192,22 +6087,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>OPAY</t>
+          <t>DTE2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>CONST</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6217,22 +6107,22 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Constant: 0</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>AP Payout</t>
+          <t>Change date - credit limit 2</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -6244,22 +6134,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ORTP</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>OKORTP</t>
+          <t>DTE3</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6269,44 +6154,44 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Mapped from OKORTP</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Customer order type</t>
+          <t>Change date - credit limit 3</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PHN2</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>OKPHN2</t>
+          <t>DTL1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6316,44 +6201,39 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Mapped from OKPHN2</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Telephone number 2</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PHNO</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>OKPHNO</t>
+          <t>DTL2</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6363,44 +6243,44 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Mapped from OKPHNO</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Telephone number 1</t>
+          <t>Change date insurance limit</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PONO</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>OKPONO</t>
+          <t>EALO</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6410,44 +6290,44 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Mapped from OKPONO</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Postal code</t>
+          <t>EAN location code</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PRIC</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>OKPRIC</t>
+          <t>ECLC</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6457,54 +6337,39 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Mapped from OKPRIC</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Price printout</t>
+          <t>Labor code - trade statistics (TST)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PYCD</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>OKPYCD</t>
+          <t>EXCD</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>MAP</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>CRS076-AR Payment Method (for customers)-PYCD.xlsx</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6514,12 +6379,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lookup Table: CRS076-AR Payment Method (for customers)-PYCD.xlsx</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Payment method - accounts receivable</t>
+          <t>Service charge</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6529,29 +6394,24 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PYDI</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>OKPYDI</t>
+          <t>EXPR</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6561,44 +6421,44 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Mapped from OKPYDI</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Payment instruction</t>
+          <t>External Prices</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PYNO</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>OKPYNO</t>
+          <t>FRE2</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6608,12 +6468,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Mapped from OKPYNO</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Payer</t>
+          <t>Statistics identity 2 customer</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6623,29 +6483,24 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>RESP</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>OKRESP</t>
+          <t>IICT</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6655,12 +6510,12 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Mapped from OKRESP</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Responsible</t>
+          <t>Interest rule</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6670,29 +6525,24 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>RMCT</t>
+          <t>IIDA</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>CONST</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Z01</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6702,44 +6552,44 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Constant: Z01</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Payment reminder rule</t>
+          <t>Invoicing interval - days</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SDST</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>OKSDST</t>
+          <t>IIMO</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6749,44 +6599,44 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Mapped from OKSDST</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>District</t>
+          <t>Invoicing interval - months</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SERC</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>OKSERC</t>
+          <t>IIYR</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6796,12 +6646,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Mapped from OKSERC</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Service code</t>
+          <t>Invoicing interval - years</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6823,22 +6673,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SMCD</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>OKSMCD</t>
+          <t>INCO</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6848,12 +6693,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Mapped from OKSMCD</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Salesperson</t>
+          <t>Insurance company</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6870,22 +6715,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>STAT</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>OKSTAT</t>
+          <t>ININ</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6895,44 +6735,44 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Mapped from OKSTAT</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Invoicing Interval</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>STMR</t>
+          <t>INLI</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>CONST</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6942,44 +6782,44 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Constant: 30</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Statement rule</t>
+          <t>Insurance limit</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>STMS</t>
+          <t>INRC</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>CONST</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6989,49 +6829,39 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Constant: 3</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Statement code</t>
+          <t>Invoice recipient</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TAXC</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>OKTAXC</t>
+          <t>INSN</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -7041,12 +6871,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Mapped from OKTAXC</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Tax code customer/address</t>
+          <t>Insurance number</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7056,29 +6886,24 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>20.0</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TDIN</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>OKTDIN</t>
+          <t>INSS</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -7088,12 +6913,12 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Mapped from OKTDIN</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Overdue invoice amount</t>
+          <t>Insurance status</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7103,34 +6928,29 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TECD</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>OKTECD</t>
+          <t>IVGP</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -7140,12 +6960,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Mapped from OKTECD</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Cash discount term</t>
+          <t>Invoicing group</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7162,22 +6982,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TECN</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>OKTECN</t>
+          <t>LSAD</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7187,12 +7002,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Mapped from OKTECN</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Tax exemption contract number</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7202,29 +7017,24 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>8.0</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TEDL</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>OKTEDL</t>
+          <t>LSID</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7234,12 +7044,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Mapped from OKTEDL</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Delivery terms</t>
+          <t>User</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7249,34 +7059,24 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TEPA</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>OKTEPA</t>
+          <t>MCOS</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>MAP</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>CRS125-Packaging Term-TEPA.xlsx</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7286,44 +7086,44 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lookup Table: CRS125-Packaging Term-TEPA.xlsx</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Packaging terms</t>
+          <t>CO number mandatory</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TEPY</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>OKTEPY</t>
+          <t>MEAL</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -7333,12 +7133,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Mapped from OKTEPY</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Payment terms</t>
+          <t>Valid media</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7348,29 +7148,24 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TFNO</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>OKTFNO</t>
+          <t>MIHP</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -7380,44 +7175,44 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Mapped from OKTFNO</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Facsimile transmission number</t>
+          <t>Minimum rental period</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>TINC</t>
+          <t>MINV</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>CONST</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Pricelist does not always include tax, so this should always be 0,  unticked</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -7427,12 +7222,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Constant: Pricelist does not always include tax, so this should always be 0,  unticked</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>VAT included</t>
+          <t>Minimum order value</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7442,34 +7237,29 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TXAP</t>
+          <t>MRTP</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>CONST</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -7479,17 +7269,17 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Constant: 1</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Tax applicable</t>
+          <t>Minimum rental type</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -7506,22 +7296,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>USL1</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>OKUSL1</t>
+          <t>MTIC</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7531,44 +7316,44 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Mapped from OKUSL1</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Changed by</t>
+          <t>Credit check - MTI</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>USL2</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>OKUSL2</t>
+          <t>NALI</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -7578,44 +7363,44 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Mapped from OKUSL2</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Changed by</t>
+          <t>Unapproved limit</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>VRNO</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>OKVRNO</t>
+          <t>ODUE</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -7625,49 +7410,44 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Mapped from OKVRNO</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>VAT registration number</t>
+          <t>Number of overdue days</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>VTCD</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>OKVTCD</t>
+          <t>OREF</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>MAP</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>CRS030-VAT Code-VTCD.xlsx</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -7677,49 +7457,39 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lookup Table: CRS030-VAT Code-VTCD.xlsx</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>VAT code</t>
+          <t>Our reference</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>30.0</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>WHLO</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>OKWHLO</t>
+          <t>OT75</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -7729,44 +7499,44 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Mapped from OKWHLO</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Self invoicing</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>YREF</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>OCUSMA SHEET OKYREF - YOUR REFERENCE 1</t>
+          <t>OT89</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -7776,34 +7546,39 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Mapped from OCUSMA SHEET OKYREF - YOUR REFERENCE 1</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Your reference 1</t>
+          <t>Check planned split</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ACEI</t>
+          <t>PADL</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7818,12 +7593,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Advance invoicing of ECI</t>
+          <t>Partial delivery</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7845,12 +7620,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ADVI</t>
+          <t>PLTB</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -7865,12 +7640,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Ship-via address</t>
+          <t>Price list table</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7880,19 +7655,19 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>AICD</t>
+          <t>POPN</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7907,39 +7682,34 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Summary invoice</t>
+          <t>Alias number</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>30.0</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>AOTP</t>
+          <t>PRDL</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7954,34 +7724,39 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Agreement order type</t>
+          <t>Print delivery information</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>BPCD</t>
+          <t>PRIC</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7996,12 +7771,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Buying pattern type</t>
+          <t>Price printout</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8023,12 +7798,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>BPEX</t>
+          <t>PRIO</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8043,12 +7818,12 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Buying pattern exception</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8070,12 +7845,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>CUTM</t>
+          <t>PRVG</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -8090,24 +7865,34 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Copy</t>
+          <t>Commission group</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DPOT</t>
+          <t>PWMT</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8122,12 +7907,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Rental depot</t>
+          <t>PIN code</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8137,24 +7922,19 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>DTL1</t>
+          <t>PYDI</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8169,34 +7949,34 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Payment instruction</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ECLC</t>
+          <t>PYGR</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8211,12 +7991,12 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Labor code - trade statistics (TST)</t>
+          <t>Credit Group</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8226,19 +8006,24 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>EXPR</t>
+          <t>PYOP</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8253,12 +8038,12 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>External Prices</t>
+          <t>Search path - payer</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8280,12 +8065,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>IIDA</t>
+          <t>QUCK</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -8300,12 +8085,12 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Invoicing interval - days</t>
+          <t>Quotation check</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8315,7 +8100,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -8327,12 +8112,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>IIMO</t>
+          <t>RAFA</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8347,12 +8132,12 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Invoicing interval - months</t>
+          <t>Rate factor</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8362,7 +8147,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -8374,12 +8159,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>IIYR</t>
+          <t>RASN</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8394,39 +8179,34 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Invoicing interval - years</t>
+          <t>Rail station</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>LSAD</t>
+          <t>RDIS</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8441,12 +8221,12 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Rental discount model</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8456,19 +8236,19 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MEAL</t>
+          <t>RPLT</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8483,12 +8263,12 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Valid media</t>
+          <t>Rent PL table</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8505,12 +8285,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MIHP</t>
+          <t>RSMC</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8525,39 +8305,34 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Minimum rental period</t>
+          <t>Rent sales pers</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MINV</t>
+          <t>RTEP</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8572,39 +8347,34 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Minimum order value</t>
+          <t>Rent Pay terms</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MRTP</t>
+          <t>RTMO</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8619,22 +8389,22 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Minimum rental type</t>
+          <t>Return months - open agreement</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -8646,12 +8416,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MTIC</t>
+          <t>RTYR</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8666,12 +8436,12 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Credit check - MTI</t>
+          <t>Return years - open agreement</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8681,7 +8451,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -8693,12 +8463,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>OT75</t>
+          <t>SECD</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8713,12 +8483,12 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Self invoicing</t>
+          <t>Delivery regrouping</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8740,12 +8510,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>OT89</t>
+          <t>SERC</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8760,12 +8530,12 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Check planned split</t>
+          <t>Service code</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8775,7 +8545,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -8787,12 +8557,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PWMT</t>
+          <t>SPLM</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8807,12 +8577,12 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>PIN code</t>
+          <t>Supply model</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -8822,19 +8592,19 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PYGR</t>
+          <t>ST75</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8849,12 +8619,12 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Credit Group</t>
+          <t>Rental rate type</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -8864,7 +8634,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -8876,12 +8646,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>QUCK</t>
+          <t>ST76</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8896,12 +8666,12 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Quotation check</t>
+          <t>Number of shifts</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -8923,12 +8693,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>RAFA</t>
+          <t>ST77</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -8943,12 +8713,12 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Rate factor</t>
+          <t>Number of days per week</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -8970,12 +8740,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>RASN</t>
+          <t>ST78</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -8990,34 +8760,39 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Rail station</t>
+          <t>Minimum days/week to invoice a</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>RDIS</t>
+          <t>TCEX</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -9032,34 +8807,39 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Rental discount model</t>
+          <t>Included in business chain</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>RPLT</t>
+          <t>TDIN</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -9074,39 +8854,39 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Rent PL table</t>
+          <t>Overdue invoice amount</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>RSMC</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>IGNORE</t>
+          <t>TEEC</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -9114,36 +8894,36 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>MCO listed but not required</t>
-        </is>
-      </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Rent sales pers</t>
+          <t>Tax exemption expiry date</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>RTEP</t>
+          <t>TRSU</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9158,12 +8938,12 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Rent Pay terms</t>
+          <t>Trade-in Supplier</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9173,19 +8953,19 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>RTMO</t>
+          <t>ULZO</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9200,39 +8980,34 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Return months - open agreement</t>
+          <t>Unloading zone</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>RTYR</t>
+          <t>USL1</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -9247,39 +9022,34 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Return years - open agreement</t>
+          <t>Changed by</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SECD</t>
+          <t>USL2</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9294,39 +9064,34 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Delivery regrouping</t>
+          <t>Changed by</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>ST75</t>
+          <t>USR1</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -9341,12 +9106,12 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Rental rate type</t>
+          <t>Credit limit 1 changed by</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -9356,24 +9121,19 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ST76</t>
+          <t>USR2</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -9388,39 +9148,34 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Number of shifts</t>
+          <t>Credit limit 2 changed by</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ST77</t>
+          <t>USR3</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -9435,39 +9190,34 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Number of days per week</t>
+          <t>Credit limit 3 changed by</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ST78</t>
+          <t>VDLA</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -9482,12 +9232,12 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Minimum days/week to invoice a</t>
+          <t>Display valid delivery addresses</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9509,12 +9259,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>CRS610_MI.xlsx</t>
+          <t>CRS610_MI</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>TRSU</t>
+          <t>YRE2</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -9529,12 +9279,12 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>MCO listed but not required</t>
+          <t>Explicitly ignored in MCO Field Usage</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Trade-in Supplier</t>
+          <t>Your reference 2</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9544,7 +9294,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>30.0</t>
         </is>
       </c>
     </row>
@@ -9592,7 +9342,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23 14:28:51</t>
+          <t>2026-09-23 14:43:34</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
